--- a/wymagania_bhp.xlsx
+++ b/wymagania_bhp.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Strona tytułowa" sheetId="3" r:id="rId1"/>
-    <sheet name="Lista kontrolna" sheetId="1" r:id="rId2"/>
+    <sheet name="Checklista" sheetId="1" r:id="rId2"/>
     <sheet name="Akty prawne" sheetId="2" r:id="rId3"/>
     <sheet name="Arkusz1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Lista kontrolna'!$A$1:$I$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Checklista!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
@@ -79,9 +79,6 @@
     <t>Ustawa z dnia 21 grudnia 2000 r. o dozorze technicznym. Dz.U. 2000 nr 122 poz. 1321</t>
   </si>
   <si>
-    <t>LISTA KONTROLNA BHP. PPOŻ, INNE</t>
-  </si>
-  <si>
     <t>Obserwacje</t>
   </si>
   <si>
@@ -886,6 +883,9 @@
   </si>
   <si>
     <t xml:space="preserve">ZAKŁAD: </t>
+  </si>
+  <si>
+    <t>Checklista</t>
   </si>
 </sst>
 </file>
@@ -1240,6 +1240,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1248,18 +1251,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1274,6 +1265,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1628,33 +1628,33 @@
   <sheetData>
     <row r="10" spans="1:5" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="26.25" x14ac:dyDescent="0.4">
       <c r="E12" s="45" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
+        <v>226</v>
+      </c>
+      <c r="J18" t="s">
         <v>227</v>
-      </c>
-      <c r="J18" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1683,17 +1683,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
+      <c r="A1" s="57" t="s">
+        <v>282</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1712,13 +1712,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>5</v>
@@ -1728,8 +1728,8 @@
       <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="53" t="s">
-        <v>24</v>
+      <c r="B3" s="59" t="s">
+        <v>23</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>10</v>
@@ -1745,7 +1745,7 @@
       <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
@@ -1760,7 +1760,7 @@
       <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="54"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="9" t="s">
         <v>15</v>
       </c>
@@ -1775,7 +1775,7 @@
       <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="54"/>
+      <c r="B6" s="60"/>
       <c r="C6" s="9" t="s">
         <v>8</v>
       </c>
@@ -1790,7 +1790,7 @@
       <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="54"/>
+      <c r="B7" s="60"/>
       <c r="C7" s="9" t="s">
         <v>9</v>
       </c>
@@ -1805,7 +1805,7 @@
       <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="54"/>
+      <c r="B8" s="60"/>
       <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
@@ -1820,7 +1820,7 @@
       <c r="A9" s="8">
         <v>7</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="9" t="s">
         <v>12</v>
       </c>
@@ -1835,7 +1835,7 @@
       <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="54"/>
+      <c r="B10" s="60"/>
       <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
@@ -1850,7 +1850,7 @@
       <c r="A11" s="8">
         <v>9</v>
       </c>
-      <c r="B11" s="55"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="9" t="s">
         <v>14</v>
       </c>
@@ -1882,11 +1882,11 @@
       <c r="A13" s="11">
         <v>1</v>
       </c>
-      <c r="B13" s="61" t="s">
-        <v>43</v>
+      <c r="B13" s="58" t="s">
+        <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="41"/>
       <c r="E13" s="18"/>
@@ -1900,9 +1900,9 @@
       <c r="A14" s="11">
         <v>2</v>
       </c>
-      <c r="B14" s="61"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="18"/>
@@ -1915,9 +1915,9 @@
       <c r="A15" s="11">
         <v>3</v>
       </c>
-      <c r="B15" s="61"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="18"/>
@@ -1930,9 +1930,9 @@
       <c r="A16" s="11">
         <v>4</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="18"/>
@@ -1945,9 +1945,9 @@
       <c r="A17" s="11">
         <v>5</v>
       </c>
-      <c r="B17" s="61"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="18"/>
@@ -1960,9 +1960,9 @@
       <c r="A18" s="11">
         <v>6</v>
       </c>
-      <c r="B18" s="61"/>
+      <c r="B18" s="58"/>
       <c r="C18" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="18"/>
@@ -1975,9 +1975,9 @@
       <c r="A19" s="11">
         <v>7</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="18"/>
@@ -1990,9 +1990,9 @@
       <c r="A20" s="11">
         <v>8</v>
       </c>
-      <c r="B20" s="61"/>
+      <c r="B20" s="58"/>
       <c r="C20" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="18"/>
@@ -2005,9 +2005,9 @@
       <c r="A21" s="11">
         <v>9</v>
       </c>
-      <c r="B21" s="61"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="18"/>
@@ -2020,9 +2020,9 @@
       <c r="A22" s="11">
         <v>10</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="18"/>
@@ -2035,9 +2035,9 @@
       <c r="A23" s="11">
         <v>11</v>
       </c>
-      <c r="B23" s="61"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="18"/>
@@ -2067,11 +2067,11 @@
       <c r="A25" s="11">
         <v>1</v>
       </c>
-      <c r="B25" s="56" t="s">
-        <v>50</v>
+      <c r="B25" s="50" t="s">
+        <v>49</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="18"/>
@@ -2084,9 +2084,9 @@
       <c r="A26" s="11">
         <v>2</v>
       </c>
-      <c r="B26" s="56"/>
+      <c r="B26" s="50"/>
       <c r="C26" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="18"/>
@@ -2099,9 +2099,9 @@
       <c r="A27" s="11">
         <v>3</v>
       </c>
-      <c r="B27" s="56"/>
+      <c r="B27" s="50"/>
       <c r="C27" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="18"/>
@@ -2114,9 +2114,9 @@
       <c r="A28" s="11">
         <v>4</v>
       </c>
-      <c r="B28" s="56"/>
+      <c r="B28" s="50"/>
       <c r="C28" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="18"/>
@@ -2129,9 +2129,9 @@
       <c r="A29" s="11">
         <v>5</v>
       </c>
-      <c r="B29" s="56"/>
+      <c r="B29" s="50"/>
       <c r="C29" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="18"/>
@@ -2144,9 +2144,9 @@
       <c r="A30" s="11">
         <v>6</v>
       </c>
-      <c r="B30" s="56"/>
+      <c r="B30" s="50"/>
       <c r="C30" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="18"/>
@@ -2176,11 +2176,11 @@
       <c r="A32" s="11">
         <v>1</v>
       </c>
-      <c r="B32" s="56" t="s">
-        <v>59</v>
+      <c r="B32" s="50" t="s">
+        <v>58</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="18"/>
@@ -2193,9 +2193,9 @@
       <c r="A33" s="11">
         <v>2</v>
       </c>
-      <c r="B33" s="56"/>
+      <c r="B33" s="50"/>
       <c r="C33" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="18"/>
@@ -2208,9 +2208,9 @@
       <c r="A34" s="11">
         <v>3</v>
       </c>
-      <c r="B34" s="56"/>
+      <c r="B34" s="50"/>
       <c r="C34" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="18"/>
@@ -2223,9 +2223,9 @@
       <c r="A35" s="11">
         <v>4</v>
       </c>
-      <c r="B35" s="56"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="18"/>
@@ -2238,9 +2238,9 @@
       <c r="A36" s="11">
         <v>5</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="50"/>
       <c r="C36" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="18"/>
@@ -2253,9 +2253,9 @@
       <c r="A37" s="11">
         <v>6</v>
       </c>
-      <c r="B37" s="56"/>
+      <c r="B37" s="50"/>
       <c r="C37" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="18"/>
@@ -2268,9 +2268,9 @@
       <c r="A38" s="11">
         <v>7</v>
       </c>
-      <c r="B38" s="56"/>
+      <c r="B38" s="50"/>
       <c r="C38" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="18"/>
@@ -2283,9 +2283,9 @@
       <c r="A39" s="11">
         <v>9</v>
       </c>
-      <c r="B39" s="56"/>
+      <c r="B39" s="50"/>
       <c r="C39" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="18"/>
@@ -2315,11 +2315,11 @@
       <c r="A41" s="11">
         <v>1</v>
       </c>
-      <c r="B41" s="56" t="s">
-        <v>69</v>
+      <c r="B41" s="50" t="s">
+        <v>68</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="18"/>
@@ -2332,9 +2332,9 @@
       <c r="A42" s="11">
         <v>2</v>
       </c>
-      <c r="B42" s="56"/>
+      <c r="B42" s="50"/>
       <c r="C42" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="18"/>
@@ -2347,9 +2347,9 @@
       <c r="A43" s="11">
         <v>3</v>
       </c>
-      <c r="B43" s="56"/>
+      <c r="B43" s="50"/>
       <c r="C43" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="18"/>
@@ -2362,9 +2362,9 @@
       <c r="A44" s="11">
         <v>4</v>
       </c>
-      <c r="B44" s="56"/>
+      <c r="B44" s="50"/>
       <c r="C44" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="18"/>
@@ -2377,9 +2377,9 @@
       <c r="A45" s="11">
         <v>5</v>
       </c>
-      <c r="B45" s="56"/>
+      <c r="B45" s="50"/>
       <c r="C45" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="18"/>
@@ -2392,9 +2392,9 @@
       <c r="A46" s="11">
         <v>6</v>
       </c>
-      <c r="B46" s="56"/>
+      <c r="B46" s="50"/>
       <c r="C46" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="18"/>
@@ -2407,9 +2407,9 @@
       <c r="A47" s="11">
         <v>7</v>
       </c>
-      <c r="B47" s="56"/>
+      <c r="B47" s="50"/>
       <c r="C47" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="18"/>
@@ -2422,9 +2422,9 @@
       <c r="A48" s="11">
         <v>8</v>
       </c>
-      <c r="B48" s="56"/>
+      <c r="B48" s="50"/>
       <c r="C48" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="18"/>
@@ -2454,11 +2454,11 @@
       <c r="A50" s="11">
         <v>1</v>
       </c>
-      <c r="B50" s="57" t="s">
-        <v>240</v>
+      <c r="B50" s="54" t="s">
+        <v>239</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="18"/>
@@ -2471,9 +2471,9 @@
       <c r="A51" s="11">
         <v>2</v>
       </c>
-      <c r="B51" s="58"/>
+      <c r="B51" s="55"/>
       <c r="C51" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="18"/>
@@ -2486,9 +2486,9 @@
       <c r="A52" s="11">
         <v>3</v>
       </c>
-      <c r="B52" s="58"/>
+      <c r="B52" s="55"/>
       <c r="C52" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="18"/>
@@ -2501,9 +2501,9 @@
       <c r="A53" s="11">
         <v>4</v>
       </c>
-      <c r="B53" s="58"/>
+      <c r="B53" s="55"/>
       <c r="C53" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="18"/>
@@ -2516,9 +2516,9 @@
       <c r="A54" s="11">
         <v>5</v>
       </c>
-      <c r="B54" s="58"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="18"/>
@@ -2531,9 +2531,9 @@
       <c r="A55" s="11">
         <v>6</v>
       </c>
-      <c r="B55" s="58"/>
+      <c r="B55" s="55"/>
       <c r="C55" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="18"/>
@@ -2546,9 +2546,9 @@
       <c r="A56" s="11">
         <v>7</v>
       </c>
-      <c r="B56" s="59"/>
+      <c r="B56" s="56"/>
       <c r="C56" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D56" s="13"/>
       <c r="E56" s="18"/>
@@ -2578,11 +2578,11 @@
       <c r="A58" s="11">
         <v>1</v>
       </c>
-      <c r="B58" s="50" t="s">
-        <v>218</v>
+      <c r="B58" s="51" t="s">
+        <v>217</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="18"/>
@@ -2595,9 +2595,9 @@
       <c r="A59" s="11">
         <v>2</v>
       </c>
-      <c r="B59" s="51"/>
+      <c r="B59" s="52"/>
       <c r="C59" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="18"/>
@@ -2610,9 +2610,9 @@
       <c r="A60" s="11">
         <v>3</v>
       </c>
-      <c r="B60" s="51"/>
+      <c r="B60" s="52"/>
       <c r="C60" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="18"/>
@@ -2625,9 +2625,9 @@
       <c r="A61" s="11">
         <v>4</v>
       </c>
-      <c r="B61" s="51"/>
+      <c r="B61" s="52"/>
       <c r="C61" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="18"/>
@@ -2640,9 +2640,9 @@
       <c r="A62" s="11">
         <v>5</v>
       </c>
-      <c r="B62" s="51"/>
+      <c r="B62" s="52"/>
       <c r="C62" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="18"/>
@@ -2655,9 +2655,9 @@
       <c r="A63" s="11">
         <v>6</v>
       </c>
-      <c r="B63" s="52"/>
+      <c r="B63" s="53"/>
       <c r="C63" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="18"/>
@@ -2687,11 +2687,11 @@
       <c r="A65" s="11">
         <v>1</v>
       </c>
-      <c r="B65" s="53" t="s">
-        <v>88</v>
+      <c r="B65" s="59" t="s">
+        <v>87</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D65" s="9"/>
       <c r="E65" s="18"/>
@@ -2704,9 +2704,9 @@
       <c r="A66" s="11">
         <v>2</v>
       </c>
-      <c r="B66" s="54"/>
+      <c r="B66" s="60"/>
       <c r="C66" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="18"/>
@@ -2719,9 +2719,9 @@
       <c r="A67" s="11">
         <v>3</v>
       </c>
-      <c r="B67" s="54"/>
+      <c r="B67" s="60"/>
       <c r="C67" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="18"/>
@@ -2734,9 +2734,9 @@
       <c r="A68" s="11">
         <v>4</v>
       </c>
-      <c r="B68" s="54"/>
+      <c r="B68" s="60"/>
       <c r="C68" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="18"/>
@@ -2749,9 +2749,9 @@
       <c r="A69" s="11">
         <v>5</v>
       </c>
-      <c r="B69" s="54"/>
+      <c r="B69" s="60"/>
       <c r="C69" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="18"/>
@@ -2764,9 +2764,9 @@
       <c r="A70" s="11">
         <v>6</v>
       </c>
-      <c r="B70" s="54"/>
+      <c r="B70" s="60"/>
       <c r="C70" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="18"/>
@@ -2779,9 +2779,9 @@
       <c r="A71" s="11">
         <v>7</v>
       </c>
-      <c r="B71" s="55"/>
+      <c r="B71" s="61"/>
       <c r="C71" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D71" s="11"/>
       <c r="E71" s="18"/>
@@ -2811,11 +2811,11 @@
       <c r="A73" s="11">
         <v>1</v>
       </c>
-      <c r="B73" s="57" t="s">
-        <v>220</v>
+      <c r="B73" s="54" t="s">
+        <v>219</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="18"/>
@@ -2828,9 +2828,9 @@
       <c r="A74" s="11">
         <v>2</v>
       </c>
-      <c r="B74" s="58"/>
+      <c r="B74" s="55"/>
       <c r="C74" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="18"/>
@@ -2843,9 +2843,9 @@
       <c r="A75" s="11">
         <v>3</v>
       </c>
-      <c r="B75" s="58"/>
+      <c r="B75" s="55"/>
       <c r="C75" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="18"/>
@@ -2858,9 +2858,9 @@
       <c r="A76" s="11">
         <v>4</v>
       </c>
-      <c r="B76" s="58"/>
+      <c r="B76" s="55"/>
       <c r="C76" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="18"/>
@@ -2873,9 +2873,9 @@
       <c r="A77" s="11">
         <v>5</v>
       </c>
-      <c r="B77" s="58"/>
+      <c r="B77" s="55"/>
       <c r="C77" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="18"/>
@@ -2888,9 +2888,9 @@
       <c r="A78" s="11">
         <v>6</v>
       </c>
-      <c r="B78" s="59"/>
+      <c r="B78" s="56"/>
       <c r="C78" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="18"/>
@@ -2920,11 +2920,11 @@
       <c r="A80" s="11">
         <v>1</v>
       </c>
-      <c r="B80" s="50" t="s">
-        <v>98</v>
+      <c r="B80" s="51" t="s">
+        <v>97</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D80" s="11"/>
       <c r="E80" s="18"/>
@@ -2937,9 +2937,9 @@
       <c r="A81" s="11">
         <v>2</v>
       </c>
-      <c r="B81" s="51"/>
+      <c r="B81" s="52"/>
       <c r="C81" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="18"/>
@@ -2952,9 +2952,9 @@
       <c r="A82" s="11">
         <v>3</v>
       </c>
-      <c r="B82" s="51"/>
+      <c r="B82" s="52"/>
       <c r="C82" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D82" s="11"/>
       <c r="E82" s="18"/>
@@ -2967,9 +2967,9 @@
       <c r="A83" s="11">
         <v>4</v>
       </c>
-      <c r="B83" s="51"/>
+      <c r="B83" s="52"/>
       <c r="C83" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="18"/>
@@ -2982,9 +2982,9 @@
       <c r="A84" s="11">
         <v>5</v>
       </c>
-      <c r="B84" s="52"/>
+      <c r="B84" s="53"/>
       <c r="C84" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D84" s="11"/>
       <c r="E84" s="18"/>
@@ -3014,11 +3014,11 @@
       <c r="A86" s="11">
         <v>1</v>
       </c>
-      <c r="B86" s="50" t="s">
-        <v>221</v>
+      <c r="B86" s="51" t="s">
+        <v>220</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="18"/>
@@ -3031,9 +3031,9 @@
       <c r="A87" s="11">
         <v>2</v>
       </c>
-      <c r="B87" s="51"/>
+      <c r="B87" s="52"/>
       <c r="C87" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="18"/>
@@ -3046,9 +3046,9 @@
       <c r="A88" s="11">
         <v>3</v>
       </c>
-      <c r="B88" s="51"/>
+      <c r="B88" s="52"/>
       <c r="C88" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="25"/>
@@ -3061,9 +3061,9 @@
       <c r="A89" s="11">
         <v>4</v>
       </c>
-      <c r="B89" s="51"/>
+      <c r="B89" s="52"/>
       <c r="C89" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="18"/>
@@ -3076,9 +3076,9 @@
       <c r="A90" s="11">
         <v>5</v>
       </c>
-      <c r="B90" s="51"/>
+      <c r="B90" s="52"/>
       <c r="C90" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="18"/>
@@ -3091,9 +3091,9 @@
       <c r="A91" s="11">
         <v>6</v>
       </c>
-      <c r="B91" s="51"/>
+      <c r="B91" s="52"/>
       <c r="C91" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D91" s="9"/>
       <c r="E91" s="18"/>
@@ -3106,9 +3106,9 @@
       <c r="A92" s="11">
         <v>7</v>
       </c>
-      <c r="B92" s="51"/>
+      <c r="B92" s="52"/>
       <c r="C92" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D92" s="9"/>
       <c r="E92" s="18"/>
@@ -3120,9 +3120,9 @@
       <c r="A93" s="11">
         <v>8</v>
       </c>
-      <c r="B93" s="51"/>
+      <c r="B93" s="52"/>
       <c r="C93" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="18"/>
@@ -3135,9 +3135,9 @@
       <c r="A94" s="11">
         <v>9</v>
       </c>
-      <c r="B94" s="51"/>
+      <c r="B94" s="52"/>
       <c r="C94" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D94" s="9"/>
       <c r="E94" s="18"/>
@@ -3150,9 +3150,9 @@
       <c r="A95" s="11">
         <v>10</v>
       </c>
-      <c r="B95" s="51"/>
+      <c r="B95" s="52"/>
       <c r="C95" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D95" s="9"/>
       <c r="E95" s="18"/>
@@ -3165,9 +3165,9 @@
       <c r="A96" s="11">
         <v>11</v>
       </c>
-      <c r="B96" s="51"/>
+      <c r="B96" s="52"/>
       <c r="C96" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D96" s="9"/>
       <c r="E96" s="18"/>
@@ -3180,9 +3180,9 @@
       <c r="A97" s="11">
         <v>12</v>
       </c>
-      <c r="B97" s="51"/>
+      <c r="B97" s="52"/>
       <c r="C97" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D97" s="9"/>
       <c r="E97" s="18"/>
@@ -3195,9 +3195,9 @@
       <c r="A98" s="11">
         <v>13</v>
       </c>
-      <c r="B98" s="51"/>
+      <c r="B98" s="52"/>
       <c r="C98" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D98" s="9"/>
       <c r="E98" s="18"/>
@@ -3210,9 +3210,9 @@
       <c r="A99" s="11">
         <v>14</v>
       </c>
-      <c r="B99" s="51"/>
+      <c r="B99" s="52"/>
       <c r="C99" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="18"/>
@@ -3225,9 +3225,9 @@
       <c r="A100" s="11">
         <v>15</v>
       </c>
-      <c r="B100" s="52"/>
+      <c r="B100" s="53"/>
       <c r="C100" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="18"/>
@@ -3257,11 +3257,11 @@
       <c r="A102" s="11">
         <v>1</v>
       </c>
-      <c r="B102" s="53" t="s">
-        <v>107</v>
+      <c r="B102" s="59" t="s">
+        <v>106</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D102" s="9"/>
       <c r="E102" s="18"/>
@@ -3274,9 +3274,9 @@
       <c r="A103" s="11">
         <v>2</v>
       </c>
-      <c r="B103" s="54"/>
+      <c r="B103" s="60"/>
       <c r="C103" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D103" s="9"/>
       <c r="E103" s="18"/>
@@ -3289,9 +3289,9 @@
       <c r="A104" s="11">
         <v>3</v>
       </c>
-      <c r="B104" s="54"/>
+      <c r="B104" s="60"/>
       <c r="C104" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D104" s="22"/>
       <c r="E104" s="18"/>
@@ -3304,9 +3304,9 @@
       <c r="A105" s="11">
         <v>4</v>
       </c>
-      <c r="B105" s="54"/>
+      <c r="B105" s="60"/>
       <c r="C105" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D105" s="9"/>
       <c r="E105" s="18"/>
@@ -3319,9 +3319,9 @@
       <c r="A106" s="11">
         <v>5</v>
       </c>
-      <c r="B106" s="54"/>
+      <c r="B106" s="60"/>
       <c r="C106" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D106" s="9"/>
       <c r="E106" s="18"/>
@@ -3334,9 +3334,9 @@
       <c r="A107" s="11">
         <v>6</v>
       </c>
-      <c r="B107" s="54"/>
+      <c r="B107" s="60"/>
       <c r="C107" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D107" s="9"/>
       <c r="E107" s="18"/>
@@ -3349,9 +3349,9 @@
       <c r="A108" s="11">
         <v>7</v>
       </c>
-      <c r="B108" s="55"/>
+      <c r="B108" s="61"/>
       <c r="C108" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D108" s="9"/>
       <c r="E108" s="18"/>
@@ -3381,11 +3381,11 @@
       <c r="A110" s="11">
         <v>1</v>
       </c>
-      <c r="B110" s="53" t="s">
-        <v>112</v>
+      <c r="B110" s="59" t="s">
+        <v>111</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D110" s="9"/>
       <c r="E110" s="18"/>
@@ -3398,9 +3398,9 @@
       <c r="A111" s="11">
         <v>2</v>
       </c>
-      <c r="B111" s="54"/>
+      <c r="B111" s="60"/>
       <c r="C111" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D111" s="9"/>
       <c r="E111" s="18"/>
@@ -3413,9 +3413,9 @@
       <c r="A112" s="11">
         <v>3</v>
       </c>
-      <c r="B112" s="54"/>
+      <c r="B112" s="60"/>
       <c r="C112" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D112" s="9"/>
       <c r="E112" s="18"/>
@@ -3428,9 +3428,9 @@
       <c r="A113" s="11">
         <v>4</v>
       </c>
-      <c r="B113" s="55"/>
+      <c r="B113" s="61"/>
       <c r="C113" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D113" s="9"/>
       <c r="E113" s="18"/>
@@ -3460,11 +3460,11 @@
       <c r="A115" s="11">
         <v>1</v>
       </c>
-      <c r="B115" s="53" t="s">
-        <v>121</v>
+      <c r="B115" s="59" t="s">
+        <v>120</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D115" s="9"/>
       <c r="E115" s="18"/>
@@ -3476,9 +3476,9 @@
       <c r="A116" s="11">
         <v>2</v>
       </c>
-      <c r="B116" s="54"/>
+      <c r="B116" s="60"/>
       <c r="C116" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D116" s="9"/>
       <c r="E116" s="18"/>
@@ -3491,9 +3491,9 @@
       <c r="A117" s="11">
         <v>3</v>
       </c>
-      <c r="B117" s="54"/>
+      <c r="B117" s="60"/>
       <c r="C117" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D117" s="9"/>
       <c r="E117" s="18"/>
@@ -3506,9 +3506,9 @@
       <c r="A118" s="11">
         <v>4</v>
       </c>
-      <c r="B118" s="54"/>
+      <c r="B118" s="60"/>
       <c r="C118" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D118" s="9"/>
       <c r="E118" s="18"/>
@@ -3521,9 +3521,9 @@
       <c r="A119" s="11">
         <v>5</v>
       </c>
-      <c r="B119" s="54"/>
+      <c r="B119" s="60"/>
       <c r="C119" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D119" s="9"/>
       <c r="E119" s="18"/>
@@ -3537,9 +3537,9 @@
       <c r="A120" s="11">
         <v>6</v>
       </c>
-      <c r="B120" s="54"/>
+      <c r="B120" s="60"/>
       <c r="C120" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D120" s="9"/>
       <c r="E120" s="18"/>
@@ -3552,9 +3552,9 @@
       <c r="A121" s="11">
         <v>7</v>
       </c>
-      <c r="B121" s="54"/>
+      <c r="B121" s="60"/>
       <c r="C121" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D121" s="9"/>
       <c r="E121" s="18"/>
@@ -3567,9 +3567,9 @@
       <c r="A122" s="11">
         <v>8</v>
       </c>
-      <c r="B122" s="55"/>
+      <c r="B122" s="61"/>
       <c r="C122" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D122" s="9"/>
       <c r="E122" s="18"/>
@@ -3599,11 +3599,11 @@
       <c r="A124" s="11">
         <v>1</v>
       </c>
-      <c r="B124" s="53" t="s">
-        <v>204</v>
+      <c r="B124" s="59" t="s">
+        <v>203</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D124" s="9"/>
       <c r="E124" s="18"/>
@@ -3616,9 +3616,9 @@
       <c r="A125" s="11">
         <v>2</v>
       </c>
-      <c r="B125" s="54"/>
+      <c r="B125" s="60"/>
       <c r="C125" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D125" s="9"/>
       <c r="E125" s="18"/>
@@ -3631,9 +3631,9 @@
       <c r="A126" s="11">
         <v>3</v>
       </c>
-      <c r="B126" s="54"/>
+      <c r="B126" s="60"/>
       <c r="C126" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D126" s="9"/>
       <c r="E126" s="18"/>
@@ -3646,9 +3646,9 @@
       <c r="A127" s="11">
         <v>4</v>
       </c>
-      <c r="B127" s="54"/>
+      <c r="B127" s="60"/>
       <c r="C127" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D127" s="9"/>
       <c r="E127" s="18"/>
@@ -3661,9 +3661,9 @@
       <c r="A128" s="11">
         <v>5</v>
       </c>
-      <c r="B128" s="54"/>
+      <c r="B128" s="60"/>
       <c r="C128" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D128" s="22"/>
       <c r="E128" s="18"/>
@@ -3676,9 +3676,9 @@
       <c r="A129" s="11">
         <v>6</v>
       </c>
-      <c r="B129" s="54"/>
+      <c r="B129" s="60"/>
       <c r="C129" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D129" s="9"/>
       <c r="E129" s="18"/>
@@ -3691,9 +3691,9 @@
       <c r="A130" s="11">
         <v>7</v>
       </c>
-      <c r="B130" s="54"/>
+      <c r="B130" s="60"/>
       <c r="C130" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D130" s="11"/>
       <c r="E130" s="18"/>
@@ -3706,9 +3706,9 @@
       <c r="A131" s="11">
         <v>8</v>
       </c>
-      <c r="B131" s="54"/>
+      <c r="B131" s="60"/>
       <c r="C131" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D131" s="9"/>
       <c r="E131" s="18"/>
@@ -3721,9 +3721,9 @@
       <c r="A132" s="11">
         <v>9</v>
       </c>
-      <c r="B132" s="55"/>
+      <c r="B132" s="61"/>
       <c r="C132" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D132" s="11"/>
       <c r="E132" s="18"/>
@@ -3753,11 +3753,11 @@
       <c r="A134" s="11">
         <v>1</v>
       </c>
-      <c r="B134" s="50" t="s">
-        <v>135</v>
+      <c r="B134" s="51" t="s">
+        <v>134</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D134" s="9"/>
       <c r="E134" s="18"/>
@@ -3770,9 +3770,9 @@
       <c r="A135" s="11">
         <v>2</v>
       </c>
-      <c r="B135" s="51"/>
+      <c r="B135" s="52"/>
       <c r="C135" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D135" s="9"/>
       <c r="E135" s="18"/>
@@ -3785,9 +3785,9 @@
       <c r="A136" s="11">
         <v>3</v>
       </c>
-      <c r="B136" s="51"/>
+      <c r="B136" s="52"/>
       <c r="C136" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D136" s="9"/>
       <c r="E136" s="18"/>
@@ -3800,9 +3800,9 @@
       <c r="A137" s="11">
         <v>4</v>
       </c>
-      <c r="B137" s="51"/>
+      <c r="B137" s="52"/>
       <c r="C137" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D137" s="9"/>
       <c r="E137" s="18"/>
@@ -3815,9 +3815,9 @@
       <c r="A138" s="11">
         <v>5</v>
       </c>
-      <c r="B138" s="52"/>
+      <c r="B138" s="53"/>
       <c r="C138" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D138" s="9"/>
       <c r="E138" s="18"/>
@@ -3847,11 +3847,11 @@
       <c r="A140" s="11">
         <v>1</v>
       </c>
-      <c r="B140" s="53" t="s">
-        <v>145</v>
+      <c r="B140" s="59" t="s">
+        <v>144</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D140" s="9"/>
       <c r="E140" s="18"/>
@@ -3864,9 +3864,9 @@
       <c r="A141" s="11">
         <v>2</v>
       </c>
-      <c r="B141" s="54"/>
+      <c r="B141" s="60"/>
       <c r="C141" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D141" s="9"/>
       <c r="E141" s="18"/>
@@ -3879,9 +3879,9 @@
       <c r="A142" s="11">
         <v>3</v>
       </c>
-      <c r="B142" s="54"/>
+      <c r="B142" s="60"/>
       <c r="C142" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D142" s="9"/>
       <c r="E142" s="18"/>
@@ -3894,9 +3894,9 @@
       <c r="A143" s="11">
         <v>4</v>
       </c>
-      <c r="B143" s="54"/>
+      <c r="B143" s="60"/>
       <c r="C143" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D143" s="9"/>
       <c r="E143" s="18"/>
@@ -3909,9 +3909,9 @@
       <c r="A144" s="11">
         <v>5</v>
       </c>
-      <c r="B144" s="54"/>
+      <c r="B144" s="60"/>
       <c r="C144" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D144" s="9"/>
       <c r="E144" s="18"/>
@@ -3924,9 +3924,9 @@
       <c r="A145" s="11">
         <v>6</v>
       </c>
-      <c r="B145" s="54"/>
+      <c r="B145" s="60"/>
       <c r="C145" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D145" s="9"/>
       <c r="E145" s="18"/>
@@ -3939,9 +3939,9 @@
       <c r="A146" s="11">
         <v>7</v>
       </c>
-      <c r="B146" s="54"/>
+      <c r="B146" s="60"/>
       <c r="C146" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D146" s="9"/>
       <c r="E146" s="18"/>
@@ -3954,9 +3954,9 @@
       <c r="A147" s="11">
         <v>8</v>
       </c>
-      <c r="B147" s="54"/>
+      <c r="B147" s="60"/>
       <c r="C147" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D147" s="9"/>
       <c r="E147" s="18"/>
@@ -3969,9 +3969,9 @@
       <c r="A148" s="11">
         <v>9</v>
       </c>
-      <c r="B148" s="54"/>
+      <c r="B148" s="60"/>
       <c r="C148" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D148" s="9"/>
       <c r="E148" s="18"/>
@@ -3984,9 +3984,9 @@
       <c r="A149" s="11">
         <v>10</v>
       </c>
-      <c r="B149" s="55"/>
+      <c r="B149" s="61"/>
       <c r="C149" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D149" s="9"/>
       <c r="E149" s="18"/>
@@ -4016,11 +4016,11 @@
       <c r="A151" s="11">
         <v>1</v>
       </c>
-      <c r="B151" s="50" t="s">
-        <v>153</v>
+      <c r="B151" s="51" t="s">
+        <v>152</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D151" s="9"/>
       <c r="E151" s="18"/>
@@ -4033,9 +4033,9 @@
       <c r="A152" s="11">
         <v>2</v>
       </c>
-      <c r="B152" s="51"/>
+      <c r="B152" s="52"/>
       <c r="C152" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D152" s="9"/>
       <c r="E152" s="18"/>
@@ -4048,9 +4048,9 @@
       <c r="A153" s="11">
         <v>3</v>
       </c>
-      <c r="B153" s="51"/>
+      <c r="B153" s="52"/>
       <c r="C153" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D153" s="9"/>
       <c r="E153" s="18"/>
@@ -4063,9 +4063,9 @@
       <c r="A154" s="11">
         <v>4</v>
       </c>
-      <c r="B154" s="51"/>
+      <c r="B154" s="52"/>
       <c r="C154" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D154" s="9"/>
       <c r="E154" s="18"/>
@@ -4078,9 +4078,9 @@
       <c r="A155" s="11">
         <v>5</v>
       </c>
-      <c r="B155" s="51"/>
+      <c r="B155" s="52"/>
       <c r="C155" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D155" s="9"/>
       <c r="E155" s="18"/>
@@ -4093,9 +4093,9 @@
       <c r="A156" s="11">
         <v>6</v>
       </c>
-      <c r="B156" s="51"/>
+      <c r="B156" s="52"/>
       <c r="C156" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D156" s="9"/>
       <c r="E156" s="18"/>
@@ -4108,9 +4108,9 @@
       <c r="A157" s="11">
         <v>7</v>
       </c>
-      <c r="B157" s="51"/>
+      <c r="B157" s="52"/>
       <c r="C157" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D157" s="9"/>
       <c r="E157" s="18"/>
@@ -4123,9 +4123,9 @@
       <c r="A158" s="11">
         <v>8</v>
       </c>
-      <c r="B158" s="52"/>
+      <c r="B158" s="53"/>
       <c r="C158" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D158" s="9"/>
       <c r="E158" s="18"/>
@@ -4155,11 +4155,11 @@
       <c r="A160" s="11">
         <v>1</v>
       </c>
-      <c r="B160" s="53" t="s">
-        <v>160</v>
+      <c r="B160" s="59" t="s">
+        <v>159</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D160" s="9"/>
       <c r="E160" s="18"/>
@@ -4172,9 +4172,9 @@
       <c r="A161" s="11">
         <v>2</v>
       </c>
-      <c r="B161" s="54"/>
+      <c r="B161" s="60"/>
       <c r="C161" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D161" s="9"/>
       <c r="E161" s="18"/>
@@ -4187,9 +4187,9 @@
       <c r="A162" s="11">
         <v>3</v>
       </c>
-      <c r="B162" s="54"/>
+      <c r="B162" s="60"/>
       <c r="C162" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D162" s="47"/>
       <c r="E162" s="18"/>
@@ -4202,9 +4202,9 @@
       <c r="A163" s="11">
         <v>4</v>
       </c>
-      <c r="B163" s="54"/>
+      <c r="B163" s="60"/>
       <c r="C163" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D163" s="9"/>
       <c r="E163" s="18"/>
@@ -4217,9 +4217,9 @@
       <c r="A164" s="11">
         <v>5</v>
       </c>
-      <c r="B164" s="54"/>
+      <c r="B164" s="60"/>
       <c r="C164" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D164" s="9"/>
       <c r="E164" s="18"/>
@@ -4232,9 +4232,9 @@
       <c r="A165" s="11">
         <v>6</v>
       </c>
-      <c r="B165" s="54"/>
+      <c r="B165" s="60"/>
       <c r="C165" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D165" s="9"/>
       <c r="E165" s="18"/>
@@ -4247,9 +4247,9 @@
       <c r="A166" s="11">
         <v>7</v>
       </c>
-      <c r="B166" s="55"/>
+      <c r="B166" s="61"/>
       <c r="C166" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D166" s="9"/>
       <c r="E166" s="18"/>
@@ -4279,11 +4279,11 @@
       <c r="A168" s="11">
         <v>1</v>
       </c>
-      <c r="B168" s="50" t="s">
-        <v>168</v>
+      <c r="B168" s="51" t="s">
+        <v>167</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D168" s="9"/>
       <c r="E168" s="18"/>
@@ -4296,9 +4296,9 @@
       <c r="A169" s="11">
         <v>2</v>
       </c>
-      <c r="B169" s="51"/>
+      <c r="B169" s="52"/>
       <c r="C169" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D169" s="9"/>
       <c r="E169" s="18"/>
@@ -4311,9 +4311,9 @@
       <c r="A170" s="11">
         <v>3</v>
       </c>
-      <c r="B170" s="51"/>
+      <c r="B170" s="52"/>
       <c r="C170" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D170" s="9"/>
       <c r="E170" s="18"/>
@@ -4326,9 +4326,9 @@
       <c r="A171" s="11">
         <v>4</v>
       </c>
-      <c r="B171" s="51"/>
+      <c r="B171" s="52"/>
       <c r="C171" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D171" s="9"/>
       <c r="E171" s="18"/>
@@ -4341,9 +4341,9 @@
       <c r="A172" s="11">
         <v>5</v>
       </c>
-      <c r="B172" s="51"/>
+      <c r="B172" s="52"/>
       <c r="C172" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D172" s="9"/>
       <c r="E172" s="18"/>
@@ -4356,9 +4356,9 @@
       <c r="A173" s="11">
         <v>6</v>
       </c>
-      <c r="B173" s="51"/>
+      <c r="B173" s="52"/>
       <c r="C173" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D173" s="9"/>
       <c r="E173" s="18"/>
@@ -4371,9 +4371,9 @@
       <c r="A174" s="11">
         <v>7</v>
       </c>
-      <c r="B174" s="52"/>
+      <c r="B174" s="53"/>
       <c r="C174" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D174" s="9"/>
       <c r="E174" s="18"/>
@@ -4403,11 +4403,11 @@
       <c r="A176" s="11">
         <v>1</v>
       </c>
-      <c r="B176" s="56" t="s">
-        <v>169</v>
+      <c r="B176" s="50" t="s">
+        <v>168</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D176" s="9"/>
       <c r="E176" s="18"/>
@@ -4420,9 +4420,9 @@
       <c r="A177" s="11">
         <v>2</v>
       </c>
-      <c r="B177" s="56"/>
+      <c r="B177" s="50"/>
       <c r="C177" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D177" s="9"/>
       <c r="E177" s="18"/>
@@ -4435,9 +4435,9 @@
       <c r="A178" s="11">
         <v>3</v>
       </c>
-      <c r="B178" s="56"/>
+      <c r="B178" s="50"/>
       <c r="C178" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D178" s="9"/>
       <c r="E178" s="18"/>
@@ -4467,11 +4467,11 @@
       <c r="A180" s="11">
         <v>1</v>
       </c>
-      <c r="B180" s="53" t="s">
-        <v>202</v>
+      <c r="B180" s="59" t="s">
+        <v>201</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D180" s="9"/>
       <c r="E180" s="18"/>
@@ -4484,9 +4484,9 @@
       <c r="A181" s="11">
         <v>2</v>
       </c>
-      <c r="B181" s="54"/>
+      <c r="B181" s="60"/>
       <c r="C181" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D181" s="9"/>
       <c r="E181" s="18"/>
@@ -4499,9 +4499,9 @@
       <c r="A182" s="11">
         <v>3</v>
       </c>
-      <c r="B182" s="54"/>
+      <c r="B182" s="60"/>
       <c r="C182" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D182" s="9"/>
       <c r="E182" s="18"/>
@@ -4514,9 +4514,9 @@
       <c r="A183" s="11">
         <v>4</v>
       </c>
-      <c r="B183" s="54"/>
+      <c r="B183" s="60"/>
       <c r="C183" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D183" s="9"/>
       <c r="E183" s="18"/>
@@ -4529,9 +4529,9 @@
       <c r="A184" s="11">
         <v>5</v>
       </c>
-      <c r="B184" s="54"/>
+      <c r="B184" s="60"/>
       <c r="C184" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D184" s="9"/>
       <c r="E184" s="18"/>
@@ -4544,9 +4544,9 @@
       <c r="A185" s="11">
         <v>6</v>
       </c>
-      <c r="B185" s="54"/>
+      <c r="B185" s="60"/>
       <c r="C185" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D185" s="9"/>
       <c r="E185" s="18"/>
@@ -4559,9 +4559,9 @@
       <c r="A186" s="11">
         <v>7</v>
       </c>
-      <c r="B186" s="54"/>
+      <c r="B186" s="60"/>
       <c r="C186" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D186" s="9"/>
       <c r="E186" s="18"/>
@@ -4574,9 +4574,9 @@
       <c r="A187" s="11">
         <v>8</v>
       </c>
-      <c r="B187" s="54"/>
+      <c r="B187" s="60"/>
       <c r="C187" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D187" s="9"/>
       <c r="E187" s="18"/>
@@ -4589,9 +4589,9 @@
       <c r="A188" s="11">
         <v>9</v>
       </c>
-      <c r="B188" s="54"/>
+      <c r="B188" s="60"/>
       <c r="C188" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D188" s="9"/>
       <c r="E188" s="18"/>
@@ -4604,9 +4604,9 @@
       <c r="A189" s="11">
         <v>10</v>
       </c>
-      <c r="B189" s="55"/>
+      <c r="B189" s="61"/>
       <c r="C189" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D189" s="9"/>
       <c r="E189" s="18"/>
@@ -4617,154 +4617,169 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B191" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B192" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="193" spans="2:4" ht="60" x14ac:dyDescent="0.25">
       <c r="B193" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="D193" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="194" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B194" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="D194" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="195" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B195" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="196" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B196" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C196" s="1" t="s">
+      <c r="D196" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B197" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="D197" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="198" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B198" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="199" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B199" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="200" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B200" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C200" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="D200" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="201" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B201" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C201" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="D201" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="202" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B202" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C202" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C202" s="1" t="s">
+      <c r="D202" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="203" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B203" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C203" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="D203" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="204" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B204" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C204" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="D204" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B168:B174"/>
+    <mergeCell ref="B180:B189"/>
+    <mergeCell ref="B124:B132"/>
+    <mergeCell ref="B134:B138"/>
+    <mergeCell ref="B140:B149"/>
+    <mergeCell ref="B151:B158"/>
+    <mergeCell ref="B160:B166"/>
+    <mergeCell ref="B176:B178"/>
+    <mergeCell ref="B102:B108"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="B115:B122"/>
+    <mergeCell ref="B65:B71"/>
+    <mergeCell ref="B73:B78"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="B86:B100"/>
     <mergeCell ref="B41:B48"/>
     <mergeCell ref="B58:B63"/>
     <mergeCell ref="B50:B56"/>
@@ -4773,21 +4788,6 @@
     <mergeCell ref="B25:B30"/>
     <mergeCell ref="B32:B39"/>
     <mergeCell ref="B3:B11"/>
-    <mergeCell ref="B102:B108"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="B115:B122"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="B73:B78"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="B86:B100"/>
-    <mergeCell ref="B168:B174"/>
-    <mergeCell ref="B180:B189"/>
-    <mergeCell ref="B124:B132"/>
-    <mergeCell ref="B134:B138"/>
-    <mergeCell ref="B140:B149"/>
-    <mergeCell ref="B151:B158"/>
-    <mergeCell ref="B160:B166"/>
-    <mergeCell ref="B176:B178"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="46" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4826,7 +4826,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4842,7 +4842,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -4850,7 +4850,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -4858,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4866,7 +4866,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4882,7 +4882,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4890,7 +4890,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -4898,7 +4898,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4906,7 +4906,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4914,7 +4914,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4922,7 +4922,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4930,7 +4930,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4938,7 +4938,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -4946,7 +4946,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4954,7 +4954,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -4962,7 +4962,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4970,7 +4970,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4978,7 +4978,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -4986,7 +4986,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -4994,7 +4994,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -5002,7 +5002,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -5010,7 +5010,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -5018,7 +5018,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -5033,57 +5033,57 @@
   <sheetData>
     <row r="2" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D2" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" s="35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/wymagania_bhp.xlsx
+++ b/wymagania_bhp.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="286">
   <si>
     <t>lp.</t>
   </si>
@@ -887,12 +887,21 @@
   <si>
     <t>Checklista</t>
   </si>
+  <si>
+    <t>https://isap.sejm.gov.pl/isap.nsf/DocDetails.xsp?id=WDU20001221321</t>
+  </si>
+  <si>
+    <t>https://isap.sejm.gov.pl/isap.nsf/DocDetails.xsp?id=WDU20180002176</t>
+  </si>
+  <si>
+    <t>https://isap.sejm.gov.pl/isap.nsf/DocDetails.xsp?id=wdu20120001468</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1028,6 +1037,14 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1110,10 +1127,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1240,9 +1258,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1251,6 +1266,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1267,17 +1294,10 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1683,17 +1703,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1728,7 +1748,7 @@
       <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="53" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -1745,7 +1765,7 @@
       <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
@@ -1760,7 +1780,7 @@
       <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="60"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="9" t="s">
         <v>15</v>
       </c>
@@ -1775,7 +1795,7 @@
       <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="9" t="s">
         <v>8</v>
       </c>
@@ -1790,7 +1810,7 @@
       <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="9" t="s">
         <v>9</v>
       </c>
@@ -1805,7 +1825,7 @@
       <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
@@ -1820,7 +1840,7 @@
       <c r="A9" s="8">
         <v>7</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="9" t="s">
         <v>12</v>
       </c>
@@ -1835,7 +1855,7 @@
       <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
@@ -1850,7 +1870,7 @@
       <c r="A11" s="8">
         <v>9</v>
       </c>
-      <c r="B11" s="61"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="9" t="s">
         <v>14</v>
       </c>
@@ -1882,7 +1902,7 @@
       <c r="A13" s="11">
         <v>1</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="61" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -1900,7 +1920,7 @@
       <c r="A14" s="11">
         <v>2</v>
       </c>
-      <c r="B14" s="58"/>
+      <c r="B14" s="61"/>
       <c r="C14" s="9" t="s">
         <v>30</v>
       </c>
@@ -1915,7 +1935,7 @@
       <c r="A15" s="11">
         <v>3</v>
       </c>
-      <c r="B15" s="58"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="31" t="s">
         <v>31</v>
       </c>
@@ -1930,7 +1950,7 @@
       <c r="A16" s="11">
         <v>4</v>
       </c>
-      <c r="B16" s="58"/>
+      <c r="B16" s="61"/>
       <c r="C16" s="9" t="s">
         <v>32</v>
       </c>
@@ -1945,7 +1965,7 @@
       <c r="A17" s="11">
         <v>5</v>
       </c>
-      <c r="B17" s="58"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="12" t="s">
         <v>33</v>
       </c>
@@ -1960,7 +1980,7 @@
       <c r="A18" s="11">
         <v>6</v>
       </c>
-      <c r="B18" s="58"/>
+      <c r="B18" s="61"/>
       <c r="C18" s="9" t="s">
         <v>34</v>
       </c>
@@ -1975,7 +1995,7 @@
       <c r="A19" s="11">
         <v>7</v>
       </c>
-      <c r="B19" s="58"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="12" t="s">
         <v>35</v>
       </c>
@@ -1990,7 +2010,7 @@
       <c r="A20" s="11">
         <v>8</v>
       </c>
-      <c r="B20" s="58"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="9" t="s">
         <v>36</v>
       </c>
@@ -2005,7 +2025,7 @@
       <c r="A21" s="11">
         <v>9</v>
       </c>
-      <c r="B21" s="58"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="9" t="s">
         <v>37</v>
       </c>
@@ -2020,7 +2040,7 @@
       <c r="A22" s="11">
         <v>10</v>
       </c>
-      <c r="B22" s="58"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="12" t="s">
         <v>38</v>
       </c>
@@ -2035,7 +2055,7 @@
       <c r="A23" s="11">
         <v>11</v>
       </c>
-      <c r="B23" s="58"/>
+      <c r="B23" s="61"/>
       <c r="C23" s="9" t="s">
         <v>39</v>
       </c>
@@ -2067,7 +2087,7 @@
       <c r="A25" s="11">
         <v>1</v>
       </c>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="56" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="9" t="s">
@@ -2084,7 +2104,7 @@
       <c r="A26" s="11">
         <v>2</v>
       </c>
-      <c r="B26" s="50"/>
+      <c r="B26" s="56"/>
       <c r="C26" s="9" t="s">
         <v>44</v>
       </c>
@@ -2099,7 +2119,7 @@
       <c r="A27" s="11">
         <v>3</v>
       </c>
-      <c r="B27" s="50"/>
+      <c r="B27" s="56"/>
       <c r="C27" s="9" t="s">
         <v>45</v>
       </c>
@@ -2114,7 +2134,7 @@
       <c r="A28" s="11">
         <v>4</v>
       </c>
-      <c r="B28" s="50"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="9" t="s">
         <v>46</v>
       </c>
@@ -2129,7 +2149,7 @@
       <c r="A29" s="11">
         <v>5</v>
       </c>
-      <c r="B29" s="50"/>
+      <c r="B29" s="56"/>
       <c r="C29" s="9" t="s">
         <v>47</v>
       </c>
@@ -2144,7 +2164,7 @@
       <c r="A30" s="11">
         <v>6</v>
       </c>
-      <c r="B30" s="50"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="9" t="s">
         <v>48</v>
       </c>
@@ -2176,7 +2196,7 @@
       <c r="A32" s="11">
         <v>1</v>
       </c>
-      <c r="B32" s="50" t="s">
+      <c r="B32" s="56" t="s">
         <v>58</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -2193,7 +2213,7 @@
       <c r="A33" s="11">
         <v>2</v>
       </c>
-      <c r="B33" s="50"/>
+      <c r="B33" s="56"/>
       <c r="C33" s="12" t="s">
         <v>51</v>
       </c>
@@ -2208,7 +2228,7 @@
       <c r="A34" s="11">
         <v>3</v>
       </c>
-      <c r="B34" s="50"/>
+      <c r="B34" s="56"/>
       <c r="C34" s="9" t="s">
         <v>52</v>
       </c>
@@ -2223,7 +2243,7 @@
       <c r="A35" s="11">
         <v>4</v>
       </c>
-      <c r="B35" s="50"/>
+      <c r="B35" s="56"/>
       <c r="C35" s="12" t="s">
         <v>53</v>
       </c>
@@ -2238,7 +2258,7 @@
       <c r="A36" s="11">
         <v>5</v>
       </c>
-      <c r="B36" s="50"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="9" t="s">
         <v>54</v>
       </c>
@@ -2253,7 +2273,7 @@
       <c r="A37" s="11">
         <v>6</v>
       </c>
-      <c r="B37" s="50"/>
+      <c r="B37" s="56"/>
       <c r="C37" s="12" t="s">
         <v>55</v>
       </c>
@@ -2268,7 +2288,7 @@
       <c r="A38" s="11">
         <v>7</v>
       </c>
-      <c r="B38" s="50"/>
+      <c r="B38" s="56"/>
       <c r="C38" s="9" t="s">
         <v>56</v>
       </c>
@@ -2283,7 +2303,7 @@
       <c r="A39" s="11">
         <v>9</v>
       </c>
-      <c r="B39" s="50"/>
+      <c r="B39" s="56"/>
       <c r="C39" s="12" t="s">
         <v>57</v>
       </c>
@@ -2315,7 +2335,7 @@
       <c r="A41" s="11">
         <v>1</v>
       </c>
-      <c r="B41" s="50" t="s">
+      <c r="B41" s="56" t="s">
         <v>68</v>
       </c>
       <c r="C41" s="12" t="s">
@@ -2332,7 +2352,7 @@
       <c r="A42" s="11">
         <v>2</v>
       </c>
-      <c r="B42" s="50"/>
+      <c r="B42" s="56"/>
       <c r="C42" s="12" t="s">
         <v>61</v>
       </c>
@@ -2347,7 +2367,7 @@
       <c r="A43" s="11">
         <v>3</v>
       </c>
-      <c r="B43" s="50"/>
+      <c r="B43" s="56"/>
       <c r="C43" s="9" t="s">
         <v>62</v>
       </c>
@@ -2362,7 +2382,7 @@
       <c r="A44" s="11">
         <v>4</v>
       </c>
-      <c r="B44" s="50"/>
+      <c r="B44" s="56"/>
       <c r="C44" s="12" t="s">
         <v>63</v>
       </c>
@@ -2377,7 +2397,7 @@
       <c r="A45" s="11">
         <v>5</v>
       </c>
-      <c r="B45" s="50"/>
+      <c r="B45" s="56"/>
       <c r="C45" s="9" t="s">
         <v>64</v>
       </c>
@@ -2392,7 +2412,7 @@
       <c r="A46" s="11">
         <v>6</v>
       </c>
-      <c r="B46" s="50"/>
+      <c r="B46" s="56"/>
       <c r="C46" s="12" t="s">
         <v>65</v>
       </c>
@@ -2407,7 +2427,7 @@
       <c r="A47" s="11">
         <v>7</v>
       </c>
-      <c r="B47" s="50"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="9" t="s">
         <v>66</v>
       </c>
@@ -2422,7 +2442,7 @@
       <c r="A48" s="11">
         <v>8</v>
       </c>
-      <c r="B48" s="50"/>
+      <c r="B48" s="56"/>
       <c r="C48" s="9" t="s">
         <v>67</v>
       </c>
@@ -2454,7 +2474,7 @@
       <c r="A50" s="11">
         <v>1</v>
       </c>
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="57" t="s">
         <v>239</v>
       </c>
       <c r="C50" s="12" t="s">
@@ -2471,7 +2491,7 @@
       <c r="A51" s="11">
         <v>2</v>
       </c>
-      <c r="B51" s="55"/>
+      <c r="B51" s="58"/>
       <c r="C51" s="12" t="s">
         <v>69</v>
       </c>
@@ -2486,7 +2506,7 @@
       <c r="A52" s="11">
         <v>3</v>
       </c>
-      <c r="B52" s="55"/>
+      <c r="B52" s="58"/>
       <c r="C52" s="12" t="s">
         <v>70</v>
       </c>
@@ -2501,7 +2521,7 @@
       <c r="A53" s="11">
         <v>4</v>
       </c>
-      <c r="B53" s="55"/>
+      <c r="B53" s="58"/>
       <c r="C53" s="12" t="s">
         <v>176</v>
       </c>
@@ -2516,7 +2536,7 @@
       <c r="A54" s="11">
         <v>5</v>
       </c>
-      <c r="B54" s="55"/>
+      <c r="B54" s="58"/>
       <c r="C54" s="12" t="s">
         <v>71</v>
       </c>
@@ -2531,7 +2551,7 @@
       <c r="A55" s="11">
         <v>6</v>
       </c>
-      <c r="B55" s="55"/>
+      <c r="B55" s="58"/>
       <c r="C55" s="12" t="s">
         <v>72</v>
       </c>
@@ -2546,7 +2566,7 @@
       <c r="A56" s="11">
         <v>7</v>
       </c>
-      <c r="B56" s="56"/>
+      <c r="B56" s="59"/>
       <c r="C56" s="12" t="s">
         <v>73</v>
       </c>
@@ -2578,7 +2598,7 @@
       <c r="A58" s="11">
         <v>1</v>
       </c>
-      <c r="B58" s="51" t="s">
+      <c r="B58" s="50" t="s">
         <v>217</v>
       </c>
       <c r="C58" s="12" t="s">
@@ -2595,7 +2615,7 @@
       <c r="A59" s="11">
         <v>2</v>
       </c>
-      <c r="B59" s="52"/>
+      <c r="B59" s="51"/>
       <c r="C59" s="12" t="s">
         <v>75</v>
       </c>
@@ -2610,7 +2630,7 @@
       <c r="A60" s="11">
         <v>3</v>
       </c>
-      <c r="B60" s="52"/>
+      <c r="B60" s="51"/>
       <c r="C60" s="9" t="s">
         <v>76</v>
       </c>
@@ -2625,7 +2645,7 @@
       <c r="A61" s="11">
         <v>4</v>
       </c>
-      <c r="B61" s="52"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="9" t="s">
         <v>77</v>
       </c>
@@ -2640,7 +2660,7 @@
       <c r="A62" s="11">
         <v>5</v>
       </c>
-      <c r="B62" s="52"/>
+      <c r="B62" s="51"/>
       <c r="C62" s="9" t="s">
         <v>78</v>
       </c>
@@ -2655,7 +2675,7 @@
       <c r="A63" s="11">
         <v>6</v>
       </c>
-      <c r="B63" s="53"/>
+      <c r="B63" s="52"/>
       <c r="C63" s="12" t="s">
         <v>79</v>
       </c>
@@ -2687,7 +2707,7 @@
       <c r="A65" s="11">
         <v>1</v>
       </c>
-      <c r="B65" s="59" t="s">
+      <c r="B65" s="53" t="s">
         <v>87</v>
       </c>
       <c r="C65" s="9" t="s">
@@ -2704,7 +2724,7 @@
       <c r="A66" s="11">
         <v>2</v>
       </c>
-      <c r="B66" s="60"/>
+      <c r="B66" s="54"/>
       <c r="C66" s="12" t="s">
         <v>81</v>
       </c>
@@ -2719,7 +2739,7 @@
       <c r="A67" s="11">
         <v>3</v>
       </c>
-      <c r="B67" s="60"/>
+      <c r="B67" s="54"/>
       <c r="C67" s="12" t="s">
         <v>82</v>
       </c>
@@ -2734,7 +2754,7 @@
       <c r="A68" s="11">
         <v>4</v>
       </c>
-      <c r="B68" s="60"/>
+      <c r="B68" s="54"/>
       <c r="C68" s="12" t="s">
         <v>83</v>
       </c>
@@ -2749,7 +2769,7 @@
       <c r="A69" s="11">
         <v>5</v>
       </c>
-      <c r="B69" s="60"/>
+      <c r="B69" s="54"/>
       <c r="C69" s="9" t="s">
         <v>84</v>
       </c>
@@ -2764,7 +2784,7 @@
       <c r="A70" s="11">
         <v>6</v>
       </c>
-      <c r="B70" s="60"/>
+      <c r="B70" s="54"/>
       <c r="C70" s="9" t="s">
         <v>85</v>
       </c>
@@ -2779,7 +2799,7 @@
       <c r="A71" s="11">
         <v>7</v>
       </c>
-      <c r="B71" s="61"/>
+      <c r="B71" s="55"/>
       <c r="C71" s="9" t="s">
         <v>86</v>
       </c>
@@ -2811,7 +2831,7 @@
       <c r="A73" s="11">
         <v>1</v>
       </c>
-      <c r="B73" s="54" t="s">
+      <c r="B73" s="57" t="s">
         <v>219</v>
       </c>
       <c r="C73" s="9" t="s">
@@ -2828,7 +2848,7 @@
       <c r="A74" s="11">
         <v>2</v>
       </c>
-      <c r="B74" s="55"/>
+      <c r="B74" s="58"/>
       <c r="C74" s="9" t="s">
         <v>89</v>
       </c>
@@ -2843,7 +2863,7 @@
       <c r="A75" s="11">
         <v>3</v>
       </c>
-      <c r="B75" s="55"/>
+      <c r="B75" s="58"/>
       <c r="C75" s="9" t="s">
         <v>90</v>
       </c>
@@ -2858,7 +2878,7 @@
       <c r="A76" s="11">
         <v>4</v>
       </c>
-      <c r="B76" s="55"/>
+      <c r="B76" s="58"/>
       <c r="C76" s="9" t="s">
         <v>91</v>
       </c>
@@ -2873,7 +2893,7 @@
       <c r="A77" s="11">
         <v>5</v>
       </c>
-      <c r="B77" s="55"/>
+      <c r="B77" s="58"/>
       <c r="C77" s="9" t="s">
         <v>92</v>
       </c>
@@ -2888,7 +2908,7 @@
       <c r="A78" s="11">
         <v>6</v>
       </c>
-      <c r="B78" s="56"/>
+      <c r="B78" s="59"/>
       <c r="C78" s="12" t="s">
         <v>190</v>
       </c>
@@ -2920,7 +2940,7 @@
       <c r="A80" s="11">
         <v>1</v>
       </c>
-      <c r="B80" s="51" t="s">
+      <c r="B80" s="50" t="s">
         <v>97</v>
       </c>
       <c r="C80" s="9" t="s">
@@ -2937,7 +2957,7 @@
       <c r="A81" s="11">
         <v>2</v>
       </c>
-      <c r="B81" s="52"/>
+      <c r="B81" s="51"/>
       <c r="C81" s="9" t="s">
         <v>94</v>
       </c>
@@ -2952,7 +2972,7 @@
       <c r="A82" s="11">
         <v>3</v>
       </c>
-      <c r="B82" s="52"/>
+      <c r="B82" s="51"/>
       <c r="C82" s="9" t="s">
         <v>95</v>
       </c>
@@ -2967,7 +2987,7 @@
       <c r="A83" s="11">
         <v>4</v>
       </c>
-      <c r="B83" s="52"/>
+      <c r="B83" s="51"/>
       <c r="C83" s="12" t="s">
         <v>240</v>
       </c>
@@ -2982,7 +3002,7 @@
       <c r="A84" s="11">
         <v>5</v>
       </c>
-      <c r="B84" s="53"/>
+      <c r="B84" s="52"/>
       <c r="C84" s="9" t="s">
         <v>96</v>
       </c>
@@ -3014,7 +3034,7 @@
       <c r="A86" s="11">
         <v>1</v>
       </c>
-      <c r="B86" s="51" t="s">
+      <c r="B86" s="50" t="s">
         <v>220</v>
       </c>
       <c r="C86" s="12" t="s">
@@ -3031,7 +3051,7 @@
       <c r="A87" s="11">
         <v>2</v>
       </c>
-      <c r="B87" s="52"/>
+      <c r="B87" s="51"/>
       <c r="C87" s="12" t="s">
         <v>178</v>
       </c>
@@ -3046,7 +3066,7 @@
       <c r="A88" s="11">
         <v>3</v>
       </c>
-      <c r="B88" s="52"/>
+      <c r="B88" s="51"/>
       <c r="C88" s="12" t="s">
         <v>179</v>
       </c>
@@ -3061,7 +3081,7 @@
       <c r="A89" s="11">
         <v>4</v>
       </c>
-      <c r="B89" s="52"/>
+      <c r="B89" s="51"/>
       <c r="C89" s="12" t="s">
         <v>99</v>
       </c>
@@ -3076,7 +3096,7 @@
       <c r="A90" s="11">
         <v>5</v>
       </c>
-      <c r="B90" s="52"/>
+      <c r="B90" s="51"/>
       <c r="C90" s="9" t="s">
         <v>180</v>
       </c>
@@ -3091,7 +3111,7 @@
       <c r="A91" s="11">
         <v>6</v>
       </c>
-      <c r="B91" s="52"/>
+      <c r="B91" s="51"/>
       <c r="C91" s="9" t="s">
         <v>181</v>
       </c>
@@ -3106,7 +3126,7 @@
       <c r="A92" s="11">
         <v>7</v>
       </c>
-      <c r="B92" s="52"/>
+      <c r="B92" s="51"/>
       <c r="C92" s="12" t="s">
         <v>189</v>
       </c>
@@ -3120,7 +3140,7 @@
       <c r="A93" s="11">
         <v>8</v>
       </c>
-      <c r="B93" s="52"/>
+      <c r="B93" s="51"/>
       <c r="C93" s="9" t="s">
         <v>188</v>
       </c>
@@ -3135,7 +3155,7 @@
       <c r="A94" s="11">
         <v>9</v>
       </c>
-      <c r="B94" s="52"/>
+      <c r="B94" s="51"/>
       <c r="C94" s="9" t="s">
         <v>187</v>
       </c>
@@ -3150,7 +3170,7 @@
       <c r="A95" s="11">
         <v>10</v>
       </c>
-      <c r="B95" s="52"/>
+      <c r="B95" s="51"/>
       <c r="C95" s="9" t="s">
         <v>186</v>
       </c>
@@ -3165,7 +3185,7 @@
       <c r="A96" s="11">
         <v>11</v>
       </c>
-      <c r="B96" s="52"/>
+      <c r="B96" s="51"/>
       <c r="C96" s="12" t="s">
         <v>185</v>
       </c>
@@ -3180,7 +3200,7 @@
       <c r="A97" s="11">
         <v>12</v>
       </c>
-      <c r="B97" s="52"/>
+      <c r="B97" s="51"/>
       <c r="C97" s="9" t="s">
         <v>221</v>
       </c>
@@ -3195,7 +3215,7 @@
       <c r="A98" s="11">
         <v>13</v>
       </c>
-      <c r="B98" s="52"/>
+      <c r="B98" s="51"/>
       <c r="C98" s="9" t="s">
         <v>182</v>
       </c>
@@ -3210,7 +3230,7 @@
       <c r="A99" s="11">
         <v>14</v>
       </c>
-      <c r="B99" s="52"/>
+      <c r="B99" s="51"/>
       <c r="C99" s="9" t="s">
         <v>183</v>
       </c>
@@ -3225,7 +3245,7 @@
       <c r="A100" s="11">
         <v>15</v>
       </c>
-      <c r="B100" s="53"/>
+      <c r="B100" s="52"/>
       <c r="C100" s="9" t="s">
         <v>184</v>
       </c>
@@ -3257,7 +3277,7 @@
       <c r="A102" s="11">
         <v>1</v>
       </c>
-      <c r="B102" s="59" t="s">
+      <c r="B102" s="53" t="s">
         <v>106</v>
       </c>
       <c r="C102" s="9" t="s">
@@ -3274,7 +3294,7 @@
       <c r="A103" s="11">
         <v>2</v>
       </c>
-      <c r="B103" s="60"/>
+      <c r="B103" s="54"/>
       <c r="C103" s="9" t="s">
         <v>101</v>
       </c>
@@ -3289,7 +3309,7 @@
       <c r="A104" s="11">
         <v>3</v>
       </c>
-      <c r="B104" s="60"/>
+      <c r="B104" s="54"/>
       <c r="C104" s="9" t="s">
         <v>102</v>
       </c>
@@ -3304,7 +3324,7 @@
       <c r="A105" s="11">
         <v>4</v>
       </c>
-      <c r="B105" s="60"/>
+      <c r="B105" s="54"/>
       <c r="C105" s="9" t="s">
         <v>99</v>
       </c>
@@ -3319,7 +3339,7 @@
       <c r="A106" s="11">
         <v>5</v>
       </c>
-      <c r="B106" s="60"/>
+      <c r="B106" s="54"/>
       <c r="C106" s="9" t="s">
         <v>103</v>
       </c>
@@ -3334,7 +3354,7 @@
       <c r="A107" s="11">
         <v>6</v>
       </c>
-      <c r="B107" s="60"/>
+      <c r="B107" s="54"/>
       <c r="C107" s="9" t="s">
         <v>104</v>
       </c>
@@ -3349,7 +3369,7 @@
       <c r="A108" s="11">
         <v>7</v>
       </c>
-      <c r="B108" s="61"/>
+      <c r="B108" s="55"/>
       <c r="C108" s="9" t="s">
         <v>105</v>
       </c>
@@ -3381,7 +3401,7 @@
       <c r="A110" s="11">
         <v>1</v>
       </c>
-      <c r="B110" s="59" t="s">
+      <c r="B110" s="53" t="s">
         <v>111</v>
       </c>
       <c r="C110" s="12" t="s">
@@ -3398,7 +3418,7 @@
       <c r="A111" s="11">
         <v>2</v>
       </c>
-      <c r="B111" s="60"/>
+      <c r="B111" s="54"/>
       <c r="C111" s="9" t="s">
         <v>108</v>
       </c>
@@ -3413,7 +3433,7 @@
       <c r="A112" s="11">
         <v>3</v>
       </c>
-      <c r="B112" s="60"/>
+      <c r="B112" s="54"/>
       <c r="C112" s="12" t="s">
         <v>109</v>
       </c>
@@ -3428,7 +3448,7 @@
       <c r="A113" s="11">
         <v>4</v>
       </c>
-      <c r="B113" s="61"/>
+      <c r="B113" s="55"/>
       <c r="C113" s="12" t="s">
         <v>110</v>
       </c>
@@ -3460,7 +3480,7 @@
       <c r="A115" s="11">
         <v>1</v>
       </c>
-      <c r="B115" s="59" t="s">
+      <c r="B115" s="53" t="s">
         <v>120</v>
       </c>
       <c r="C115" s="9" t="s">
@@ -3476,7 +3496,7 @@
       <c r="A116" s="11">
         <v>2</v>
       </c>
-      <c r="B116" s="60"/>
+      <c r="B116" s="54"/>
       <c r="C116" s="9" t="s">
         <v>113</v>
       </c>
@@ -3491,7 +3511,7 @@
       <c r="A117" s="11">
         <v>3</v>
       </c>
-      <c r="B117" s="60"/>
+      <c r="B117" s="54"/>
       <c r="C117" s="12" t="s">
         <v>114</v>
       </c>
@@ -3506,7 +3526,7 @@
       <c r="A118" s="11">
         <v>4</v>
       </c>
-      <c r="B118" s="60"/>
+      <c r="B118" s="54"/>
       <c r="C118" s="9" t="s">
         <v>115</v>
       </c>
@@ -3521,7 +3541,7 @@
       <c r="A119" s="11">
         <v>5</v>
       </c>
-      <c r="B119" s="60"/>
+      <c r="B119" s="54"/>
       <c r="C119" s="9" t="s">
         <v>116</v>
       </c>
@@ -3537,7 +3557,7 @@
       <c r="A120" s="11">
         <v>6</v>
       </c>
-      <c r="B120" s="60"/>
+      <c r="B120" s="54"/>
       <c r="C120" s="9" t="s">
         <v>117</v>
       </c>
@@ -3552,7 +3572,7 @@
       <c r="A121" s="11">
         <v>7</v>
       </c>
-      <c r="B121" s="60"/>
+      <c r="B121" s="54"/>
       <c r="C121" s="9" t="s">
         <v>118</v>
       </c>
@@ -3567,7 +3587,7 @@
       <c r="A122" s="11">
         <v>8</v>
       </c>
-      <c r="B122" s="61"/>
+      <c r="B122" s="55"/>
       <c r="C122" s="9" t="s">
         <v>119</v>
       </c>
@@ -3599,7 +3619,7 @@
       <c r="A124" s="11">
         <v>1</v>
       </c>
-      <c r="B124" s="59" t="s">
+      <c r="B124" s="53" t="s">
         <v>203</v>
       </c>
       <c r="C124" s="12" t="s">
@@ -3616,7 +3636,7 @@
       <c r="A125" s="11">
         <v>2</v>
       </c>
-      <c r="B125" s="60"/>
+      <c r="B125" s="54"/>
       <c r="C125" s="12" t="s">
         <v>122</v>
       </c>
@@ -3631,7 +3651,7 @@
       <c r="A126" s="11">
         <v>3</v>
       </c>
-      <c r="B126" s="60"/>
+      <c r="B126" s="54"/>
       <c r="C126" s="12" t="s">
         <v>123</v>
       </c>
@@ -3646,7 +3666,7 @@
       <c r="A127" s="11">
         <v>4</v>
       </c>
-      <c r="B127" s="60"/>
+      <c r="B127" s="54"/>
       <c r="C127" s="9" t="s">
         <v>124</v>
       </c>
@@ -3661,7 +3681,7 @@
       <c r="A128" s="11">
         <v>5</v>
       </c>
-      <c r="B128" s="60"/>
+      <c r="B128" s="54"/>
       <c r="C128" s="9" t="s">
         <v>125</v>
       </c>
@@ -3676,7 +3696,7 @@
       <c r="A129" s="11">
         <v>6</v>
       </c>
-      <c r="B129" s="60"/>
+      <c r="B129" s="54"/>
       <c r="C129" s="9" t="s">
         <v>126</v>
       </c>
@@ -3691,7 +3711,7 @@
       <c r="A130" s="11">
         <v>7</v>
       </c>
-      <c r="B130" s="60"/>
+      <c r="B130" s="54"/>
       <c r="C130" s="9" t="s">
         <v>127</v>
       </c>
@@ -3706,7 +3726,7 @@
       <c r="A131" s="11">
         <v>8</v>
       </c>
-      <c r="B131" s="60"/>
+      <c r="B131" s="54"/>
       <c r="C131" s="9" t="s">
         <v>128</v>
       </c>
@@ -3721,7 +3741,7 @@
       <c r="A132" s="11">
         <v>9</v>
       </c>
-      <c r="B132" s="61"/>
+      <c r="B132" s="55"/>
       <c r="C132" s="9" t="s">
         <v>129</v>
       </c>
@@ -3753,7 +3773,7 @@
       <c r="A134" s="11">
         <v>1</v>
       </c>
-      <c r="B134" s="51" t="s">
+      <c r="B134" s="50" t="s">
         <v>134</v>
       </c>
       <c r="C134" s="12" t="s">
@@ -3770,7 +3790,7 @@
       <c r="A135" s="11">
         <v>2</v>
       </c>
-      <c r="B135" s="52"/>
+      <c r="B135" s="51"/>
       <c r="C135" s="9" t="s">
         <v>131</v>
       </c>
@@ -3785,7 +3805,7 @@
       <c r="A136" s="11">
         <v>3</v>
       </c>
-      <c r="B136" s="52"/>
+      <c r="B136" s="51"/>
       <c r="C136" s="9" t="s">
         <v>132</v>
       </c>
@@ -3800,7 +3820,7 @@
       <c r="A137" s="11">
         <v>4</v>
       </c>
-      <c r="B137" s="52"/>
+      <c r="B137" s="51"/>
       <c r="C137" s="9" t="s">
         <v>133</v>
       </c>
@@ -3815,7 +3835,7 @@
       <c r="A138" s="11">
         <v>5</v>
       </c>
-      <c r="B138" s="53"/>
+      <c r="B138" s="52"/>
       <c r="C138" s="9" t="s">
         <v>192</v>
       </c>
@@ -3847,7 +3867,7 @@
       <c r="A140" s="11">
         <v>1</v>
       </c>
-      <c r="B140" s="59" t="s">
+      <c r="B140" s="53" t="s">
         <v>144</v>
       </c>
       <c r="C140" s="12" t="s">
@@ -3864,7 +3884,7 @@
       <c r="A141" s="11">
         <v>2</v>
       </c>
-      <c r="B141" s="60"/>
+      <c r="B141" s="54"/>
       <c r="C141" s="9" t="s">
         <v>136</v>
       </c>
@@ -3879,7 +3899,7 @@
       <c r="A142" s="11">
         <v>3</v>
       </c>
-      <c r="B142" s="60"/>
+      <c r="B142" s="54"/>
       <c r="C142" s="9" t="s">
         <v>137</v>
       </c>
@@ -3894,7 +3914,7 @@
       <c r="A143" s="11">
         <v>4</v>
       </c>
-      <c r="B143" s="60"/>
+      <c r="B143" s="54"/>
       <c r="C143" s="12" t="s">
         <v>138</v>
       </c>
@@ -3909,7 +3929,7 @@
       <c r="A144" s="11">
         <v>5</v>
       </c>
-      <c r="B144" s="60"/>
+      <c r="B144" s="54"/>
       <c r="C144" s="9" t="s">
         <v>139</v>
       </c>
@@ -3924,7 +3944,7 @@
       <c r="A145" s="11">
         <v>6</v>
       </c>
-      <c r="B145" s="60"/>
+      <c r="B145" s="54"/>
       <c r="C145" s="9" t="s">
         <v>140</v>
       </c>
@@ -3939,7 +3959,7 @@
       <c r="A146" s="11">
         <v>7</v>
       </c>
-      <c r="B146" s="60"/>
+      <c r="B146" s="54"/>
       <c r="C146" s="9" t="s">
         <v>141</v>
       </c>
@@ -3954,7 +3974,7 @@
       <c r="A147" s="11">
         <v>8</v>
       </c>
-      <c r="B147" s="60"/>
+      <c r="B147" s="54"/>
       <c r="C147" s="9" t="s">
         <v>142</v>
       </c>
@@ -3969,7 +3989,7 @@
       <c r="A148" s="11">
         <v>9</v>
       </c>
-      <c r="B148" s="60"/>
+      <c r="B148" s="54"/>
       <c r="C148" s="9" t="s">
         <v>143</v>
       </c>
@@ -3984,7 +4004,7 @@
       <c r="A149" s="11">
         <v>10</v>
       </c>
-      <c r="B149" s="61"/>
+      <c r="B149" s="55"/>
       <c r="C149" s="9" t="s">
         <v>194</v>
       </c>
@@ -4016,7 +4036,7 @@
       <c r="A151" s="11">
         <v>1</v>
       </c>
-      <c r="B151" s="51" t="s">
+      <c r="B151" s="50" t="s">
         <v>152</v>
       </c>
       <c r="C151" s="12" t="s">
@@ -4033,7 +4053,7 @@
       <c r="A152" s="11">
         <v>2</v>
       </c>
-      <c r="B152" s="52"/>
+      <c r="B152" s="51"/>
       <c r="C152" s="12" t="s">
         <v>146</v>
       </c>
@@ -4048,7 +4068,7 @@
       <c r="A153" s="11">
         <v>3</v>
       </c>
-      <c r="B153" s="52"/>
+      <c r="B153" s="51"/>
       <c r="C153" s="9" t="s">
         <v>147</v>
       </c>
@@ -4063,7 +4083,7 @@
       <c r="A154" s="11">
         <v>4</v>
       </c>
-      <c r="B154" s="52"/>
+      <c r="B154" s="51"/>
       <c r="C154" s="9" t="s">
         <v>148</v>
       </c>
@@ -4078,7 +4098,7 @@
       <c r="A155" s="11">
         <v>5</v>
       </c>
-      <c r="B155" s="52"/>
+      <c r="B155" s="51"/>
       <c r="C155" s="9" t="s">
         <v>149</v>
       </c>
@@ -4093,7 +4113,7 @@
       <c r="A156" s="11">
         <v>6</v>
       </c>
-      <c r="B156" s="52"/>
+      <c r="B156" s="51"/>
       <c r="C156" s="9" t="s">
         <v>150</v>
       </c>
@@ -4108,7 +4128,7 @@
       <c r="A157" s="11">
         <v>7</v>
       </c>
-      <c r="B157" s="52"/>
+      <c r="B157" s="51"/>
       <c r="C157" s="9" t="s">
         <v>151</v>
       </c>
@@ -4123,7 +4143,7 @@
       <c r="A158" s="11">
         <v>8</v>
       </c>
-      <c r="B158" s="53"/>
+      <c r="B158" s="52"/>
       <c r="C158" s="9" t="s">
         <v>195</v>
       </c>
@@ -4155,7 +4175,7 @@
       <c r="A160" s="11">
         <v>1</v>
       </c>
-      <c r="B160" s="59" t="s">
+      <c r="B160" s="53" t="s">
         <v>159</v>
       </c>
       <c r="C160" s="12" t="s">
@@ -4172,7 +4192,7 @@
       <c r="A161" s="11">
         <v>2</v>
       </c>
-      <c r="B161" s="60"/>
+      <c r="B161" s="54"/>
       <c r="C161" s="12" t="s">
         <v>154</v>
       </c>
@@ -4187,7 +4207,7 @@
       <c r="A162" s="11">
         <v>3</v>
       </c>
-      <c r="B162" s="60"/>
+      <c r="B162" s="54"/>
       <c r="C162" s="12" t="s">
         <v>155</v>
       </c>
@@ -4202,7 +4222,7 @@
       <c r="A163" s="11">
         <v>4</v>
       </c>
-      <c r="B163" s="60"/>
+      <c r="B163" s="54"/>
       <c r="C163" s="12" t="s">
         <v>218</v>
       </c>
@@ -4217,7 +4237,7 @@
       <c r="A164" s="11">
         <v>5</v>
       </c>
-      <c r="B164" s="60"/>
+      <c r="B164" s="54"/>
       <c r="C164" s="9" t="s">
         <v>156</v>
       </c>
@@ -4232,7 +4252,7 @@
       <c r="A165" s="11">
         <v>6</v>
       </c>
-      <c r="B165" s="60"/>
+      <c r="B165" s="54"/>
       <c r="C165" s="9" t="s">
         <v>157</v>
       </c>
@@ -4247,7 +4267,7 @@
       <c r="A166" s="11">
         <v>7</v>
       </c>
-      <c r="B166" s="61"/>
+      <c r="B166" s="55"/>
       <c r="C166" s="9" t="s">
         <v>158</v>
       </c>
@@ -4279,7 +4299,7 @@
       <c r="A168" s="11">
         <v>1</v>
       </c>
-      <c r="B168" s="51" t="s">
+      <c r="B168" s="50" t="s">
         <v>167</v>
       </c>
       <c r="C168" s="12" t="s">
@@ -4296,7 +4316,7 @@
       <c r="A169" s="11">
         <v>2</v>
       </c>
-      <c r="B169" s="52"/>
+      <c r="B169" s="51"/>
       <c r="C169" s="12" t="s">
         <v>161</v>
       </c>
@@ -4311,7 +4331,7 @@
       <c r="A170" s="11">
         <v>3</v>
       </c>
-      <c r="B170" s="52"/>
+      <c r="B170" s="51"/>
       <c r="C170" s="12" t="s">
         <v>162</v>
       </c>
@@ -4326,7 +4346,7 @@
       <c r="A171" s="11">
         <v>4</v>
       </c>
-      <c r="B171" s="52"/>
+      <c r="B171" s="51"/>
       <c r="C171" s="9" t="s">
         <v>163</v>
       </c>
@@ -4341,7 +4361,7 @@
       <c r="A172" s="11">
         <v>5</v>
       </c>
-      <c r="B172" s="52"/>
+      <c r="B172" s="51"/>
       <c r="C172" s="9" t="s">
         <v>164</v>
       </c>
@@ -4356,7 +4376,7 @@
       <c r="A173" s="11">
         <v>6</v>
       </c>
-      <c r="B173" s="52"/>
+      <c r="B173" s="51"/>
       <c r="C173" s="9" t="s">
         <v>165</v>
       </c>
@@ -4371,7 +4391,7 @@
       <c r="A174" s="11">
         <v>7</v>
       </c>
-      <c r="B174" s="53"/>
+      <c r="B174" s="52"/>
       <c r="C174" s="9" t="s">
         <v>166</v>
       </c>
@@ -4403,7 +4423,7 @@
       <c r="A176" s="11">
         <v>1</v>
       </c>
-      <c r="B176" s="50" t="s">
+      <c r="B176" s="56" t="s">
         <v>168</v>
       </c>
       <c r="C176" s="12" t="s">
@@ -4420,7 +4440,7 @@
       <c r="A177" s="11">
         <v>2</v>
       </c>
-      <c r="B177" s="50"/>
+      <c r="B177" s="56"/>
       <c r="C177" s="12" t="s">
         <v>222</v>
       </c>
@@ -4435,7 +4455,7 @@
       <c r="A178" s="11">
         <v>3</v>
       </c>
-      <c r="B178" s="50"/>
+      <c r="B178" s="56"/>
       <c r="C178" s="9" t="s">
         <v>223</v>
       </c>
@@ -4467,7 +4487,7 @@
       <c r="A180" s="11">
         <v>1</v>
       </c>
-      <c r="B180" s="59" t="s">
+      <c r="B180" s="53" t="s">
         <v>201</v>
       </c>
       <c r="C180" s="9" t="s">
@@ -4484,7 +4504,7 @@
       <c r="A181" s="11">
         <v>2</v>
       </c>
-      <c r="B181" s="60"/>
+      <c r="B181" s="54"/>
       <c r="C181" s="12" t="s">
         <v>170</v>
       </c>
@@ -4499,7 +4519,7 @@
       <c r="A182" s="11">
         <v>3</v>
       </c>
-      <c r="B182" s="60"/>
+      <c r="B182" s="54"/>
       <c r="C182" s="12" t="s">
         <v>171</v>
       </c>
@@ -4514,7 +4534,7 @@
       <c r="A183" s="11">
         <v>4</v>
       </c>
-      <c r="B183" s="60"/>
+      <c r="B183" s="54"/>
       <c r="C183" s="12" t="s">
         <v>172</v>
       </c>
@@ -4529,7 +4549,7 @@
       <c r="A184" s="11">
         <v>5</v>
       </c>
-      <c r="B184" s="60"/>
+      <c r="B184" s="54"/>
       <c r="C184" s="12" t="s">
         <v>173</v>
       </c>
@@ -4544,7 +4564,7 @@
       <c r="A185" s="11">
         <v>6</v>
       </c>
-      <c r="B185" s="60"/>
+      <c r="B185" s="54"/>
       <c r="C185" s="12" t="s">
         <v>174</v>
       </c>
@@ -4559,7 +4579,7 @@
       <c r="A186" s="11">
         <v>7</v>
       </c>
-      <c r="B186" s="60"/>
+      <c r="B186" s="54"/>
       <c r="C186" s="9" t="s">
         <v>224</v>
       </c>
@@ -4574,7 +4594,7 @@
       <c r="A187" s="11">
         <v>8</v>
       </c>
-      <c r="B187" s="60"/>
+      <c r="B187" s="54"/>
       <c r="C187" s="9" t="s">
         <v>198</v>
       </c>
@@ -4589,7 +4609,7 @@
       <c r="A188" s="11">
         <v>9</v>
       </c>
-      <c r="B188" s="60"/>
+      <c r="B188" s="54"/>
       <c r="C188" s="9" t="s">
         <v>199</v>
       </c>
@@ -4604,7 +4624,7 @@
       <c r="A189" s="11">
         <v>10</v>
       </c>
-      <c r="B189" s="61"/>
+      <c r="B189" s="55"/>
       <c r="C189" s="9" t="s">
         <v>200</v>
       </c>
@@ -4765,6 +4785,21 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="B58:B63"/>
+    <mergeCell ref="B50:B56"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="B32:B39"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="B102:B108"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="B115:B122"/>
+    <mergeCell ref="B65:B71"/>
+    <mergeCell ref="B73:B78"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="B86:B100"/>
     <mergeCell ref="B168:B174"/>
     <mergeCell ref="B180:B189"/>
     <mergeCell ref="B124:B132"/>
@@ -4773,21 +4808,6 @@
     <mergeCell ref="B151:B158"/>
     <mergeCell ref="B160:B166"/>
     <mergeCell ref="B176:B178"/>
-    <mergeCell ref="B102:B108"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="B115:B122"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="B73:B78"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="B86:B100"/>
-    <mergeCell ref="B41:B48"/>
-    <mergeCell ref="B58:B63"/>
-    <mergeCell ref="B50:B56"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="B32:B39"/>
-    <mergeCell ref="B3:B11"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="46" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4799,13 +4819,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="98.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="65.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>16</v>
       </c>
@@ -4813,31 +4834,40 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="C2" s="62" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="C3" s="62" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="62" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -4845,7 +4875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -4853,7 +4883,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -4861,7 +4891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -4869,7 +4899,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -4877,7 +4907,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -4885,7 +4915,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -4893,7 +4923,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>11</v>
       </c>
@@ -4901,7 +4931,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -4909,7 +4939,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>13</v>
       </c>
@@ -4917,7 +4947,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>14</v>
       </c>
@@ -4925,7 +4955,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>15</v>
       </c>
@@ -5022,6 +5052,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1"/>
+    <hyperlink ref="C4" r:id="rId2"/>
+    <hyperlink ref="C2" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
